--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2109-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2109-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF24C645-40D6-4CC7-A47F-4AEDECD30656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3D9B8FD-A1B5-4E34-A975-8111DD19FC8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{EAC8052C-24D5-474C-8608-EDAFBBC50619}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{06F5E560-295D-43A4-BEE6-38DC7F365F33}"/>
   </bookViews>
   <sheets>
     <sheet name="2109-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1478,21 +1478,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDD95864-AF76-4284-B65D-BB3A65258DEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAEDB266-80B4-4C14-AD70-3D42698A3B58}">
   <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="6" width="8" customWidth="1"/>
-    <col min="7" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="6" width="10" customWidth="1"/>
+    <col min="7" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1520,7 +1520,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1550,7 +1550,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1596,7 +1596,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1646,7 +1646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>3.06</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>8.09</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1978,7 +1978,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>5.48</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2144,7 +2144,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2364,7 +2364,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2420,7 +2420,7 @@
         <v>2.91</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2530,7 +2530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="37">
         <v>2019</v>
       </c>
@@ -2584,7 +2584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2018</v>
       </c>
@@ -2638,7 +2638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2017</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>1.78</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2016</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2015</v>
       </c>
@@ -2800,7 +2800,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2014</v>
       </c>
@@ -2854,7 +2854,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2013</v>
       </c>
@@ -2908,7 +2908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2012</v>
       </c>
@@ -2962,7 +2962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2011</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2010</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2009</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2008</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>1.34</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2007</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2006</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2005</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>4.29</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2004</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2003</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>5.15</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2002</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>2.99</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2001</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>9.27</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2000</v>
       </c>
@@ -3610,7 +3610,7 @@
         <v>9.8000000000000007</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>1999</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>1998</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>1997</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>1996</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>1995</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>1994</v>
       </c>
@@ -3934,7 +3934,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>1993</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>1992</v>
       </c>
@@ -4042,7 +4042,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>1991</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1989</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1983</v>
       </c>
@@ -4204,7 +4204,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1981</v>
       </c>
@@ -4258,7 +4258,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>1979</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1976</v>
       </c>
@@ -4366,7 +4366,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37" t="s">
         <v>45</v>
       </c>
